--- a/Soft/Dimer.xlsx
+++ b/Soft/Dimer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2.Datos\Electronica\Proyectos\Microchip\Git\Casandra\Soft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A35B6A0-065A-487E-BDA5-B848F6846371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E5944B-266B-4D90-893E-05CCF5787EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comandos" sheetId="2" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="504">
   <si>
     <t>Valor</t>
   </si>
@@ -1671,9 +1671,6 @@
     <t>0 a 10</t>
   </si>
   <si>
-    <t>Modos de encendido del led</t>
-  </si>
-  <si>
     <t>Velocidad del modo de encendido</t>
   </si>
   <si>
@@ -1761,9 +1758,6 @@
     <t>Reset / Reconect / Exec</t>
   </si>
   <si>
-    <t>1, 2, 3, 4</t>
-  </si>
-  <si>
     <t>Estado de Switch Porton</t>
   </si>
   <si>
@@ -1773,7 +1767,67 @@
     <t>Intensidad de encendido de luz LED</t>
   </si>
   <si>
-    <t>Modos de encendido del LED</t>
+    <t>de</t>
+  </si>
+  <si>
+    <t>hasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vuelve a </t>
+  </si>
+  <si>
+    <t>"Normal", "Respira", "Flash"</t>
+  </si>
+  <si>
+    <t>"Normal", "OlaRGB", "FlashRGB". "Respira", "Flash"</t>
+  </si>
+  <si>
+    <t>1, 2, 3. 4 y 5</t>
+  </si>
+  <si>
+    <t>1, 2 y 3</t>
+  </si>
+  <si>
+    <t>Resp</t>
+  </si>
+  <si>
+    <t>de 0 a 25</t>
+  </si>
+  <si>
+    <t>de 25 a Max+25</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>--max</t>
+  </si>
+  <si>
+    <t>llega a 0</t>
+  </si>
+  <si>
+    <t>de max+25 a max+50</t>
+  </si>
+  <si>
+    <t>mantiene max</t>
+  </si>
+  <si>
+    <t>mantiene 0</t>
+  </si>
+  <si>
+    <t>llega a max</t>
+  </si>
+  <si>
+    <t>++max</t>
+  </si>
+  <si>
+    <t>de max+50 a 2max+50</t>
+  </si>
+  <si>
+    <t>si max 100</t>
+  </si>
+  <si>
+    <t>251 = 0</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2080,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2197,6 +2251,12 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor theme="8" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2860,7 +2920,7 @@
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3460,6 +3520,28 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Incorrecto" xfId="2" builtinId="27"/>
@@ -4768,13 +4850,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>19046</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>752473</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>180976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4816,13 +4898,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -4865,6 +4947,67 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>670560</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB3396-A3AD-3B67-F371-8E4DB664769C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6941820" y="2819400"/>
+          <a:ext cx="5539740" cy="2354580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7314,6 +7457,12 @@
       <c r="G10" s="70" t="s">
         <v>131</v>
       </c>
+      <c r="J10" s="225">
+        <v>178</v>
+      </c>
+      <c r="K10" s="225" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="145">
@@ -9822,10 +9971,10 @@
       </c>
       <c r="D56" s="180"/>
       <c r="E56" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G56" s="29" t="s">
         <v>307</v>
@@ -11521,10 +11670,10 @@
       </c>
       <c r="D119" s="180"/>
       <c r="E119" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F119" s="25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G119" s="29" t="s">
         <v>307</v>
@@ -12410,10 +12559,10 @@
       </c>
       <c r="D152" s="180"/>
       <c r="E152" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F152" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G152" s="29" t="s">
         <v>307</v>
@@ -12612,10 +12761,10 @@
       </c>
       <c r="D160" s="183"/>
       <c r="E160" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F160" s="185" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G160" s="183" t="s">
         <v>307</v>
@@ -12872,10 +13021,10 @@
       </c>
       <c r="D170" s="184"/>
       <c r="E170" s="183" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F170" s="185" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G170" s="183" t="s">
         <v>307</v>
@@ -13047,10 +13196,10 @@
       </c>
       <c r="D177" s="184"/>
       <c r="E177" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F177" s="185" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G177" s="183" t="s">
         <v>307</v>
@@ -13122,10 +13271,10 @@
       </c>
       <c r="D180" s="29"/>
       <c r="E180" s="29" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="F180" s="25" t="s">
-        <v>451</v>
+        <v>487</v>
       </c>
       <c r="G180" s="29" t="s">
         <v>307</v>
@@ -13150,7 +13299,7 @@
         <v>450</v>
       </c>
       <c r="F181" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G181" s="29" t="s">
         <v>307</v>
@@ -13703,13 +13852,13 @@
         <v>388</v>
       </c>
       <c r="D202" s="29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E202" s="29" t="s">
         <v>374</v>
       </c>
       <c r="F202" s="25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G202" s="29" t="s">
         <v>307</v>
@@ -13736,7 +13885,7 @@
         <v>374</v>
       </c>
       <c r="F203" s="25" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G203" s="29" t="s">
         <v>307</v>
@@ -13763,7 +13912,7 @@
         <v>374</v>
       </c>
       <c r="F204" s="25" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G204" s="29" t="s">
         <v>307</v>
@@ -13790,7 +13939,7 @@
         <v>374</v>
       </c>
       <c r="F205" s="25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G205" s="29" t="s">
         <v>307</v>
@@ -13817,7 +13966,7 @@
         <v>374</v>
       </c>
       <c r="F206" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G206" s="29" t="s">
         <v>307</v>
@@ -13844,7 +13993,7 @@
         <v>374</v>
       </c>
       <c r="F207" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G207" s="29" t="s">
         <v>307</v>
@@ -13871,7 +14020,7 @@
         <v>374</v>
       </c>
       <c r="F208" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G208" s="29" t="s">
         <v>307</v>
@@ -13898,7 +14047,7 @@
         <v>374</v>
       </c>
       <c r="F209" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G209" s="29" t="s">
         <v>307</v>
@@ -14028,10 +14177,10 @@
       </c>
       <c r="D214" s="29"/>
       <c r="E214" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F214" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G214" s="29" t="s">
         <v>307</v>
@@ -14053,7 +14202,7 @@
       </c>
       <c r="D215" s="175"/>
       <c r="E215" s="175" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F215" s="177" t="s">
         <v>428</v>
@@ -14077,7 +14226,7 @@
         <v>427</v>
       </c>
       <c r="E216" s="29" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F216" s="25" t="s">
         <v>429</v>
@@ -14098,13 +14247,13 @@
         <v>425</v>
       </c>
       <c r="C217" s="29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E217" s="29" t="s">
         <v>275</v>
       </c>
       <c r="F217" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G217" s="29" t="s">
         <v>307</v>
@@ -14122,14 +14271,14 @@
         <v>425</v>
       </c>
       <c r="C218" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D218" s="29"/>
       <c r="E218" s="29" t="s">
         <v>275</v>
       </c>
       <c r="F218" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G218" s="29" t="s">
         <v>307</v>
@@ -14151,10 +14300,10 @@
       </c>
       <c r="D219" s="183"/>
       <c r="E219" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F219" s="185" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G219" s="183" t="s">
         <v>307</v>
@@ -14169,17 +14318,17 @@
         <v>53</v>
       </c>
       <c r="B220" s="175" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C220" s="175" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D220" s="175"/>
       <c r="E220" s="175" t="s">
         <v>275</v>
       </c>
       <c r="F220" s="25" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G220" s="175" t="s">
         <v>307</v>
@@ -14194,17 +14343,17 @@
         <v>53</v>
       </c>
       <c r="B221" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C221" s="29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D221" s="29"/>
       <c r="E221" s="29" t="s">
         <v>302</v>
       </c>
       <c r="F221" s="25" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G221" s="29" t="s">
         <v>307</v>
@@ -14219,17 +14368,17 @@
         <v>53</v>
       </c>
       <c r="B222" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C222" s="29" t="s">
         <v>448</v>
       </c>
       <c r="D222" s="29"/>
       <c r="E222" s="29" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="F222" s="25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G222" s="29" t="s">
         <v>307</v>
@@ -14244,7 +14393,7 @@
         <v>53</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C223" s="29" t="s">
         <v>449</v>
@@ -14254,7 +14403,7 @@
         <v>302</v>
       </c>
       <c r="F223" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G223" s="29" t="s">
         <v>307</v>
@@ -14269,17 +14418,17 @@
         <v>53</v>
       </c>
       <c r="B224" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C224" s="29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D224" s="29"/>
       <c r="E224" s="29" t="s">
         <v>275</v>
       </c>
       <c r="F224" s="25" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G224" s="29" t="s">
         <v>307</v>
@@ -14294,7 +14443,7 @@
         <v>53</v>
       </c>
       <c r="B225" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C225" s="29" t="s">
         <v>318</v>
@@ -14319,17 +14468,17 @@
         <v>53</v>
       </c>
       <c r="B226" s="183" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C226" s="183" t="s">
         <v>248</v>
       </c>
       <c r="D226" s="183"/>
       <c r="E226" s="183" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F226" s="185" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G226" s="183" t="s">
         <v>307</v>
@@ -18072,259 +18221,501 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:H24"/>
+  <dimension ref="B2:U23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="9.33203125" style="29" customWidth="1"/>
+    <col min="13" max="13" width="4.5546875" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" style="25"/>
+    <col min="19" max="19" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>27</v>
+      </c>
+      <c r="G3" s="126" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="127" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" s="30">
+        <v>0</v>
+      </c>
+      <c r="M3" s="224">
+        <v>1</v>
+      </c>
+      <c r="N3" s="222" t="s">
+        <v>483</v>
+      </c>
+      <c r="O3" s="223">
+        <f>L3-0</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="219" t="s">
+        <v>502</v>
+      </c>
+      <c r="R3" s="219"/>
+      <c r="S3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C4" s="1">
-        <v>27</v>
-      </c>
-      <c r="G4" s="126" t="s">
-        <v>236</v>
-      </c>
-      <c r="H4" s="127" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+        <f>C3-3</f>
+        <v>24</v>
+      </c>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119">
+        <v>0</v>
+      </c>
+      <c r="H4" s="124"/>
+      <c r="L4" s="30">
+        <v>255</v>
+      </c>
+      <c r="M4" s="224"/>
+      <c r="N4" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O4" s="221">
+        <f>L4-0</f>
+        <v>255</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>25</v>
+      </c>
+      <c r="S4" t="s">
+        <v>491</v>
+      </c>
+      <c r="T4" t="s">
+        <v>493</v>
+      </c>
+      <c r="U4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C5" s="1">
-        <f>C4-3</f>
-        <v>24</v>
+        <f t="shared" ref="C5:C12" si="0">C4-3</f>
+        <v>21</v>
       </c>
       <c r="F5" s="118"/>
-      <c r="G5" s="119">
+      <c r="G5" s="120">
+        <v>3</v>
+      </c>
+      <c r="H5" s="123">
+        <v>0.9</v>
+      </c>
+      <c r="L5" s="30">
+        <v>256</v>
+      </c>
+      <c r="M5" s="224">
+        <v>2</v>
+      </c>
+      <c r="N5" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="O5" s="221">
+        <f>L5-256</f>
         <v>0</v>
       </c>
-      <c r="H5" s="124"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <v>25</v>
+      </c>
+      <c r="R5">
+        <v>125</v>
+      </c>
+      <c r="S5" t="s">
+        <v>492</v>
+      </c>
+      <c r="T5" s="226" t="s">
+        <v>494</v>
+      </c>
+      <c r="U5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" ref="C6:C13" si="0">C5-3</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="F6" s="118"/>
       <c r="G6" s="120">
-        <v>3</v>
-      </c>
-      <c r="H6" s="123">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="H6" s="125"/>
+      <c r="L6" s="30">
+        <v>511</v>
+      </c>
+      <c r="M6" s="224"/>
+      <c r="N6" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O6" s="221">
+        <f>L6-256</f>
+        <v>255</v>
+      </c>
+      <c r="Q6">
+        <v>125</v>
+      </c>
+      <c r="R6">
+        <v>150</v>
+      </c>
+      <c r="S6" t="s">
+        <v>496</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" s="118"/>
       <c r="G7" s="120">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H7" s="125"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="L7" s="30">
+        <v>512</v>
+      </c>
+      <c r="M7" s="224">
+        <v>3</v>
+      </c>
+      <c r="N7" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="O7" s="221">
+        <f>L7-512</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>150</v>
+      </c>
+      <c r="R7">
+        <v>250</v>
+      </c>
+      <c r="S7" t="s">
+        <v>501</v>
+      </c>
+      <c r="T7" s="226" t="s">
+        <v>500</v>
+      </c>
+      <c r="U7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F8" s="118"/>
       <c r="G8" s="120">
-        <v>11</v>
-      </c>
-      <c r="H8" s="125"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="H8" s="123">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="30">
+        <v>767</v>
+      </c>
+      <c r="M8" s="224"/>
+      <c r="N8" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O8" s="221">
+        <f>L8-512</f>
+        <v>255</v>
+      </c>
+      <c r="R8" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F9" s="118"/>
       <c r="G9" s="120">
-        <v>15</v>
-      </c>
-      <c r="H9" s="123">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="H9" s="125"/>
+      <c r="L9" s="30">
+        <v>768</v>
+      </c>
+      <c r="M9" s="224">
+        <v>4</v>
+      </c>
+      <c r="N9" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="O9" s="221">
+        <f>L9-768</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="118"/>
       <c r="G10" s="120">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H10" s="125"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="L10" s="30">
+        <v>1023</v>
+      </c>
+      <c r="M10" s="224"/>
+      <c r="N10" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O10" s="221">
+        <f>L10-768</f>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="118"/>
       <c r="G11" s="120">
-        <v>23</v>
-      </c>
-      <c r="H11" s="125"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="C12" s="1">
+        <v>27</v>
+      </c>
+      <c r="H11" s="123">
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="30">
+        <v>1024</v>
+      </c>
+      <c r="M11" s="224">
+        <v>5</v>
+      </c>
+      <c r="N11" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="O11" s="221">
+        <f>L11-1024</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="118"/>
       <c r="G12" s="120">
-        <v>27</v>
-      </c>
-      <c r="H12" s="123">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="H12" s="125"/>
+      <c r="L12" s="30">
+        <v>1279</v>
+      </c>
+      <c r="M12" s="224"/>
+      <c r="N12" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O12" s="221">
+        <f>L12-1024</f>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="6">
         <v>0</v>
       </c>
+      <c r="C13" s="7">
+        <v>95</v>
+      </c>
       <c r="F13" s="118"/>
-      <c r="G13" s="120">
-        <v>31</v>
-      </c>
-      <c r="H13" s="125"/>
-    </row>
-    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="6">
+      <c r="G13" s="121">
+        <v>35</v>
+      </c>
+      <c r="H13" s="112" t="s">
+        <v>238</v>
+      </c>
+      <c r="L13" s="30">
+        <v>1280</v>
+      </c>
+      <c r="M13" s="224">
+        <v>6</v>
+      </c>
+      <c r="N13" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="O13" s="221">
+        <f>L13-1280</f>
         <v>0</v>
       </c>
-      <c r="C14" s="7">
-        <v>95</v>
-      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="F14" s="118"/>
-      <c r="G14" s="121">
-        <v>35</v>
-      </c>
-      <c r="H14" s="112" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="122">
+        <v>39</v>
+      </c>
+      <c r="H14" s="124"/>
+      <c r="L14" s="30">
+        <v>1535</v>
+      </c>
+      <c r="M14" s="224"/>
+      <c r="N14" s="220" t="s">
+        <v>484</v>
+      </c>
+      <c r="O14" s="221">
+        <f>L14-1280</f>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="F15" s="118"/>
-      <c r="G15" s="122">
-        <v>39</v>
-      </c>
-      <c r="H15" s="124"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G15" s="120">
+        <v>43</v>
+      </c>
+      <c r="H15" s="123">
+        <v>0.9</v>
+      </c>
+      <c r="L15" s="30">
+        <v>1536</v>
+      </c>
+      <c r="M15" s="31"/>
+      <c r="N15" s="222" t="s">
+        <v>485</v>
+      </c>
+      <c r="O15" s="223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="F16" s="118"/>
       <c r="G16" s="120">
-        <v>43</v>
-      </c>
-      <c r="H16" s="123">
-        <v>0.9</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H16" s="125"/>
     </row>
     <row r="17" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F17" s="118"/>
       <c r="G17" s="120">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H17" s="125"/>
     </row>
     <row r="18" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F18" s="118"/>
       <c r="G18" s="120">
-        <v>51</v>
-      </c>
-      <c r="H18" s="125"/>
+        <v>55</v>
+      </c>
+      <c r="H18" s="123">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="19" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F19" s="118"/>
       <c r="G19" s="120">
-        <v>55</v>
-      </c>
-      <c r="H19" s="123">
-        <v>0.5</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="H19" s="125"/>
     </row>
     <row r="20" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F20" s="118"/>
       <c r="G20" s="120">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H20" s="125"/>
     </row>
     <row r="21" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F21" s="118"/>
       <c r="G21" s="120">
-        <v>63</v>
-      </c>
-      <c r="H21" s="125"/>
+        <v>67</v>
+      </c>
+      <c r="H21" s="123">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="22" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F22" s="118"/>
       <c r="G22" s="120">
-        <v>67</v>
-      </c>
-      <c r="H22" s="123">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" spans="6:8" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="H22" s="125"/>
+    </row>
+    <row r="23" spans="6:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F23" s="118"/>
-      <c r="G23" s="120">
-        <v>71</v>
-      </c>
-      <c r="H23" s="125"/>
-    </row>
-    <row r="24" spans="6:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F24" s="118"/>
-      <c r="G24" s="121">
+      <c r="G23" s="121">
         <v>75</v>
       </c>
-      <c r="H24" s="112" t="s">
+      <c r="H23" s="112" t="s">
         <v>237</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M13:M14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
